--- a/artfynd/A 42748-2024 artfynd.xlsx
+++ b/artfynd/A 42748-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97905169</v>
+        <v>103907518</v>
       </c>
       <c r="B2" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>4787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gryt, Sörgryten, Nrk</t>
+          <t>Sörgryten, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478202.0615338078</v>
+        <v>478331</v>
       </c>
       <c r="R2" t="n">
-        <v>6564799.82292927</v>
+        <v>6564970</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,69 +754,63 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103907518</v>
+        <v>104127652</v>
       </c>
       <c r="B3" t="n">
-        <v>90339</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörgryten, Nrk</t>
+          <t>Sörgrytenområdet, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478331.7444485821</v>
+        <v>478314</v>
       </c>
       <c r="R3" t="n">
-        <v>6564970.561650102</v>
+        <v>6564611</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +866,425 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>74585583</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sörgryten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478237</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6564889</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-05-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-05-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97905169</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gryt, Sörgryten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478202</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6564800</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-01-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-01-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104127654</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sörgrytenområdet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478282</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6564598</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>74585581</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sörgryten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478224</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6564879</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-05-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>20 x 20 cm</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
